--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Eléments de l'entête d'un document contenant les données les informations générales et nécessaires à la gestion du document (identification et type du document, patient/usager, auteur, évènement documenté, etc...</t>
+    <t>Eléments de l'entête d'un document contenant les informations générales et nécessaires à la gestion du document (identification et type du document, patient/usager, auteur, évènement documenté, etc...).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -234,10 +234,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>*</t>
+    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -247,10 +244,13 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>EnteteDocument.identifiantUniqueDocument</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -286,7 +286,7 @@
     <t>Titre du document.</t>
   </si>
   <si>
-    <t>EnteteDocument.dateDeCreation</t>
+    <t>EnteteDocument.dateDeCreationDocument</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -296,7 +296,11 @@
     <t>Date de création du document.</t>
   </si>
   <si>
-    <t>EnteteDocument.niveauConfidentialite</t>
+    <t>EnteteDocument.niveauConfidentialiteDocument</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
   </si>
   <si>
     <t>Niveau de confidentialité du document.</t>
@@ -308,7 +312,7 @@
     <t>Langue principale du document.</t>
   </si>
   <si>
-    <t>EnteteDocument.identifiantDuLotDeVersions</t>
+    <t>EnteteDocument.identifiantLotDeVersionsDocument</t>
   </si>
   <si>
     <t>Identifiant du lot de versions du même document.</t>
@@ -416,10 +420,10 @@
     <t>Participant, différent de l'auteur, du responsable, de l'opérateur de saisie, de l'informateur ou du destinataire.</t>
   </si>
   <si>
-    <t>EnteteDocument.associationPrescription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/AssociationPrescription
+    <t>EnteteDocument.prescription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Prescription
 </t>
   </si>
   <si>
@@ -436,10 +440,10 @@
     <t>Evènement documenté et notamment le cadre d'exercice.</t>
   </si>
   <si>
-    <t>EnteteDocument.documentReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DocumentReference
+    <t>EnteteDocument.documentDeReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DocumentDeReference
 </t>
   </si>
   <si>
@@ -456,10 +460,10 @@
     <t>Consentement associé au document.</t>
   </si>
   <si>
-    <t>EnteteDocument.associationPriseEncharge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/AssociationPriseEncharge
+    <t>EnteteDocument.priseEncharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PriseEncharge
 </t>
   </si>
   <si>
@@ -768,40 +772,40 @@
   <dimension ref="A1:AJ26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.453125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="87.0859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.8125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="42.453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -931,19 +935,19 @@
         <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1000,13 +1004,13 @@
         <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AG2" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AH2" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>72</v>
@@ -1017,10 +1021,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1028,10 +1032,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>72</v>
@@ -1100,13 +1104,13 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>72</v>
@@ -1128,10 +1132,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1203,10 +1207,10 @@
         <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1228,10 +1232,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1303,10 +1307,10 @@
         <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
@@ -1328,10 +1332,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1403,10 +1407,10 @@
         <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>72</v>
@@ -1428,10 +1432,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1503,10 +1507,10 @@
         <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>72</v>
@@ -1528,10 +1532,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
@@ -1543,13 +1547,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1603,10 +1607,10 @@
         <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>72</v>
@@ -1617,10 +1621,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1628,10 +1632,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>72</v>
@@ -1643,13 +1647,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1700,13 +1704,13 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>72</v>
@@ -1717,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1728,10 +1732,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
@@ -1746,10 +1750,10 @@
         <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1800,13 +1804,13 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
@@ -1817,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1828,10 +1832,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>72</v>
@@ -1846,10 +1850,10 @@
         <v>87</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1900,13 +1904,13 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>72</v>
@@ -1917,10 +1921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1928,10 +1932,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
@@ -1943,13 +1947,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2000,13 +2004,13 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>72</v>
@@ -2017,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2028,10 +2032,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -2043,13 +2047,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2100,13 +2104,13 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2128,10 +2132,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
@@ -2143,13 +2147,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2200,13 +2204,13 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
@@ -2217,10 +2221,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2228,10 +2232,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>72</v>
@@ -2243,13 +2247,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2300,13 +2304,13 @@
         <v>72</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>72</v>
@@ -2317,10 +2321,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2328,10 +2332,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>72</v>
@@ -2343,13 +2347,13 @@
         <v>72</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2400,13 +2404,13 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>72</v>
@@ -2417,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2428,10 +2432,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>72</v>
@@ -2443,13 +2447,13 @@
         <v>72</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2500,13 +2504,13 @@
         <v>72</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>72</v>
@@ -2517,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2528,10 +2532,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>72</v>
@@ -2543,13 +2547,13 @@
         <v>72</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2600,13 +2604,13 @@
         <v>72</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>72</v>
@@ -2617,10 +2621,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2628,10 +2632,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>72</v>
@@ -2643,13 +2647,13 @@
         <v>72</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2700,13 +2704,13 @@
         <v>72</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>72</v>
@@ -2717,10 +2721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2728,10 +2732,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>72</v>
@@ -2743,13 +2747,13 @@
         <v>72</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2800,13 +2804,13 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>72</v>
@@ -2817,10 +2821,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2828,10 +2832,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>72</v>
@@ -2843,13 +2847,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2900,13 +2904,13 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>72</v>
@@ -2917,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2928,10 +2932,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>72</v>
@@ -2943,13 +2947,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3000,13 +3004,13 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>72</v>
@@ -3017,10 +3021,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3028,10 +3032,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>72</v>
@@ -3043,13 +3047,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3100,13 +3104,13 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>72</v>
@@ -3117,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3128,10 +3132,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>72</v>
@@ -3143,13 +3147,13 @@
         <v>72</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3200,13 +3204,13 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>72</v>
@@ -3217,10 +3221,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3228,10 +3232,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>72</v>
@@ -3243,13 +3247,13 @@
         <v>72</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3300,13 +3304,13 @@
         <v>72</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>72</v>
@@ -3317,10 +3321,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3328,10 +3332,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>72</v>
@@ -3343,13 +3347,13 @@
         <v>72</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3400,13 +3404,13 @@
         <v>72</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>72</v>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -333,7 +333,7 @@
     <t>EnteteDocument.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Patient
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PatientUsager
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-EnteteDocument.xlsx
+++ b/main/ig/StructureDefinition-EnteteDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
